--- a/week19/MyFlow_工数見積もり.xlsx
+++ b/week19/MyFlow_工数見積もり.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sssha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sssha\Desktop\myflow\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F1DF9999E0100E7FFAFA47346BC3D5F666E0A385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54BC4BA0-DB89-4F67-A66F-9715A26C208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <r>
       <rPr>
@@ -77,31 +77,217 @@
     <t>No</t>
   </si>
   <si>
-    <t>機能</t>
+    <t>ユーザーストーリー（機能）</t>
+  </si>
+  <si>
+    <t>スプリント</t>
   </si>
   <si>
     <t>工数（日）</t>
   </si>
   <si>
-    <t>タスク作成時に期限を設定できる</t>
-  </si>
-  <si>
-    <t>締め切りが近いタスク順に並び替えることができる</t>
-  </si>
-  <si>
-    <t>就活用、学校用に分けて表示することができる</t>
-  </si>
-  <si>
-    <t>並び替え処理（②のために必要な共通処理）</t>
-  </si>
-  <si>
-    <t>タスクを編集（更新）できる</t>
+    <t>①</t>
+  </si>
+  <si>
+    <t>タスクに期限を設定できる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>スプリント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Week22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>②</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>締め切りの近いタスク順に並び替えられる（並び替え処理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日＋ボタン配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日）</t>
+    </r>
+  </si>
+  <si>
+    <t>③</t>
+  </si>
+  <si>
+    <t>就活用・学校用で分けて表示できる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>スプリント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Week23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>④</t>
+  </si>
+  <si>
+    <t>タスクの名前を直せる</t>
+  </si>
+  <si>
+    <t>⑤</t>
   </si>
   <si>
     <t>タスクを削除できる</t>
   </si>
   <si>
-    <t>合計</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>スプリント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Week24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>実装工数の小計</t>
+  </si>
+  <si>
+    <t>確認作業（動作確認・調整）</t>
+  </si>
+  <si>
+    <t>合計（実装＋確認作業）</t>
   </si>
   <si>
     <r>
@@ -111,7 +297,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>使える日数（平日換算・</t>
+      <t>使える日数（</t>
     </r>
     <r>
       <rPr>
@@ -129,36 +315,100 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>週間）</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>余裕日数</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
+      <t>週間・平日換算）</t>
+    </r>
+  </si>
+  <si>
+    <t>余裕日数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※青字は入力値（使える日数：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Week22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>の平日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Week20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>のスプリント計画より）。設計費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日は含まない。</t>
     </r>
   </si>
 </sst>
@@ -166,7 +416,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,13 +463,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Noto Sans CJK SC"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
@@ -231,6 +481,23 @@
     <font>
       <i/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -288,28 +555,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -574,22 +848,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.399999999999999">
+    <row r="1" spans="1:4" ht="17.399999999999999">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -599,105 +875,141 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4">
-        <v>1</v>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4">
+    <row r="5" spans="1:4">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9">
+        <f>SUM(D4:D8)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8">
-        <f>SUM(C4:C9)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10">
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9">
+        <f>D9+D10</f>
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="10">
-        <f>C12-C10</f>
-        <v>3</v>
+    <row r="13" spans="1:4">
+      <c r="B13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="12">
+        <f>D13-D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <phoneticPr fontId="12"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/week19/MyFlow_工数見積もり.xlsx
+++ b/week19/MyFlow_工数見積もり.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sssha\Desktop\myflow\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sssha\Desktop\techmeets\myflow\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54BC4BA0-DB89-4F67-A66F-9715A26C208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBC047BE-E648-4057-BE75-10F973872B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <r>
       <rPr>
@@ -61,7 +61,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>MVP</t>
+      <t>Must</t>
     </r>
     <r>
       <rPr>
@@ -70,14 +70,14 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>最終版）</t>
+      <t>）</t>
     </r>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>ユーザーストーリー（機能）</t>
+    <t>機能</t>
   </si>
   <si>
     <t>スプリント</t>
@@ -230,7 +230,7 @@
     <t>④</t>
   </si>
   <si>
-    <t>タスクの名前を直せる</t>
+    <t>タスクを完了にできる</t>
   </si>
   <si>
     <t>⑤</t>
@@ -384,15 +384,57 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Week20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>のスプリント計画より）。設計費</t>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>日）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※設計費</t>
     </r>
     <r>
       <rPr>
@@ -408,8 +450,43 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>日は含まない。</t>
-    </r>
+      <t>日、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Should</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>（⑥〜⑨）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Could</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>（⑩〜⑬）は含まない。</t>
+    </r>
+  </si>
+  <si>
+    <t>※デプロイの工数は、技術選定が決まってから追加する。</t>
   </si>
 </sst>
 </file>
@@ -848,11 +925,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="2" max="2" width="78" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
@@ -1003,6 +1080,16 @@
     <row r="16" spans="1:4">
       <c r="B16" s="13" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
